--- a/Data/FY2027/Budget.xlsx
+++ b/Data/FY2027/Budget.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saad.qaiser_karandaa\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saad.qaiser_karandaa\Desktop\Dashboard\DATA\FY2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68A97C8-EAAF-4BF1-AAFA-2DBB102E60A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{498F69FF-D61F-4408-9521-6DD9AFA662F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C0CDB9EF-DF96-4D5D-A877-12178ED5EE09}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget" sheetId="1" r:id="rId1"/>
@@ -18,18 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Budget!$A$1:$J$232</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -948,17 +937,14 @@
     <t>ERP Solution</t>
   </si>
   <si>
-    <t>Furniture and fixtures</t>
+    <t xml:space="preserve">Furniture and fixtures </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.##;\(#,##0.##\)"/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -967,13 +953,134 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -982,11 +1089,185 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE4EC"/>
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -994,22 +1275,219 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1032,44 +1510,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -1096,14 +1574,32 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -1130,6 +1626,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1141,222 +1655,205 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1417D1F6-F6B4-48AE-8FD9-EF6F6F73215F}">
   <dimension ref="A1:J232"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="10" width="13" customWidth="1"/>
+    <col min="1" max="1" width="26.85546875" customWidth="1"/>
+    <col min="2" max="2" width="43.5703125" customWidth="1"/>
+    <col min="3" max="3" width="69" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="99.28515625" customWidth="1"/>
+    <col min="6" max="6" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G2" s="2">
@@ -1373,22 +1870,25 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2">
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="2">
@@ -1396,19 +1896,22 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2">
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
         <v>0</v>
       </c>
       <c r="I4" s="2">
@@ -1419,19 +1922,20 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G5" s="2">
@@ -1448,16 +1952,18 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E6" t="s">
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G6" s="2">
@@ -1466,53 +1972,56 @@
       <c r="H6" s="2">
         <v>1000000</v>
       </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2">
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E7" t="s">
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G7" s="2">
         <v>9800000</v>
       </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G8" s="2">
@@ -1529,19 +2038,20 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G9" s="2">
@@ -1558,19 +2068,20 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G10" s="2">
@@ -1587,19 +2098,20 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G11" s="2">
@@ -1616,19 +2128,20 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C12" t="s">
+      <c r="B12" s="1"/>
+      <c r="C12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G12" s="2">
@@ -1645,13 +2158,16 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F13" t="s">
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G13" s="2">
@@ -1668,13 +2184,16 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C14" t="s">
+      <c r="B14" s="1"/>
+      <c r="C14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F14" t="s">
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G14" s="2">
@@ -1691,13 +2210,16 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C15" t="s">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F15" t="s">
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G15" s="2">
@@ -1714,36 +2236,42 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C16" t="s">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="2">
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="2">
         <v>100000000</v>
       </c>
-      <c r="I16" s="2">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2">
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C17" t="s">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F17" t="s">
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G17" s="2">
@@ -1760,39 +2288,45 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C18" t="s">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F18" t="s">
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G18" s="2">
         <v>1000000</v>
       </c>
-      <c r="H18" s="2">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2">
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C19" t="s">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F19" t="s">
-        <v>35</v>
-      </c>
-      <c r="G19" s="2">
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="1">
         <v>0</v>
       </c>
       <c r="H19" s="2">
@@ -1806,13 +2340,16 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C20" t="s">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F20" t="s">
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G20" s="2">
@@ -1829,13 +2366,16 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C21" t="s">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F21" t="s">
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G21" s="2">
@@ -1852,28 +2392,29 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C22" t="s">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G22" s="2">
         <v>548750</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="1">
         <v>548750</v>
       </c>
-      <c r="I22" s="2">
+      <c r="I22" s="1">
         <v>548750</v>
       </c>
       <c r="J22" s="2">
@@ -1881,28 +2422,29 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="A23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C23" t="s">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G23" s="2">
         <v>375000</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="1">
         <v>375000</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23" s="1">
         <v>375000</v>
       </c>
       <c r="J23" s="2">
@@ -1910,19 +2452,20 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C24" t="s">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G24" s="2">
@@ -1939,86 +2482,89 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="A25" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C25" t="s">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G25" s="2">
         <v>1000000</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="1">
         <v>21500000</v>
       </c>
-      <c r="I25" s="2">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2">
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="A26" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C26" t="s">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G26" s="2">
         <v>12500000</v>
       </c>
-      <c r="H26" s="2">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2">
-        <v>0</v>
-      </c>
-      <c r="J26" s="2">
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C27" t="s">
+      <c r="B27" s="1"/>
+      <c r="C27" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F27" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27" s="2">
-        <v>0</v>
-      </c>
-      <c r="H27" s="2">
+      <c r="F27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
         <v>3250000</v>
       </c>
-      <c r="I27" s="2">
+      <c r="I27" s="1">
         <v>1625000</v>
       </c>
       <c r="J27" s="2">
@@ -2026,28 +2572,29 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="A28" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C28" t="s">
+      <c r="B28" s="1"/>
+      <c r="C28" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G28" s="2">
         <v>5000000</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H28" s="1">
         <v>5000000</v>
       </c>
-      <c r="I28" s="2">
+      <c r="I28" s="1">
         <v>5000000</v>
       </c>
       <c r="J28" s="2">
@@ -2055,28 +2602,29 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C29" t="s">
+      <c r="B29" s="1"/>
+      <c r="C29" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G29" s="2">
         <v>548750</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29" s="1">
         <v>548750</v>
       </c>
-      <c r="I29" s="2">
+      <c r="I29" s="1">
         <v>548750</v>
       </c>
       <c r="J29" s="2">
@@ -2084,28 +2632,29 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C30" t="s">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G30" s="2">
         <v>375000</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30" s="1">
         <v>375000</v>
       </c>
-      <c r="I30" s="2">
+      <c r="I30" s="1">
         <v>375000</v>
       </c>
       <c r="J30" s="2">
@@ -2113,19 +2662,20 @@
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C31" t="s">
+      <c r="B31" s="1"/>
+      <c r="C31" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G31" s="2">
@@ -2142,54 +2692,57 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A32" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C32" t="s">
+      <c r="B32" s="1"/>
+      <c r="C32" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G32" s="2">
         <v>580000</v>
       </c>
-      <c r="H32" s="2">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2">
-        <v>0</v>
-      </c>
-      <c r="J32" s="2">
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="A33" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C33" t="s">
+      <c r="B33" s="1"/>
+      <c r="C33" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E33" t="s">
+      <c r="D33" s="1"/>
+      <c r="E33" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F33" t="s">
-        <v>12</v>
-      </c>
-      <c r="G33" s="2">
-        <v>0</v>
-      </c>
-      <c r="H33" s="2">
+      <c r="F33" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
         <v>4500000</v>
       </c>
-      <c r="I33" s="2">
+      <c r="I33" s="1">
         <v>4500000</v>
       </c>
       <c r="J33" s="2">
@@ -2197,28 +2750,29 @@
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="A34" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C34" t="s">
+      <c r="B34" s="1"/>
+      <c r="C34" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G34" s="2">
         <v>1250000</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34" s="1">
         <v>1250000</v>
       </c>
-      <c r="I34" s="2">
+      <c r="I34" s="1">
         <v>1250000</v>
       </c>
       <c r="J34" s="2">
@@ -2226,28 +2780,29 @@
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="A35" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C35" t="s">
+      <c r="B35" s="1"/>
+      <c r="C35" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G35" s="2">
         <v>1075000</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H35" s="1">
         <v>1525000</v>
       </c>
-      <c r="I35" s="2">
+      <c r="I35" s="1">
         <v>725000</v>
       </c>
       <c r="J35" s="2">
@@ -2255,83 +2810,87 @@
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C36" t="s">
+      <c r="B36" s="1"/>
+      <c r="C36" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G36" s="2">
         <v>5525000</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H36" s="1">
         <v>2490000</v>
       </c>
-      <c r="I36" s="2">
-        <v>0</v>
-      </c>
-      <c r="J36" s="2">
+      <c r="I36" s="1">
+        <v>0</v>
+      </c>
+      <c r="J36" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="A37" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C37" t="s">
+      <c r="B37" s="1"/>
+      <c r="C37" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G37" s="2">
         <v>2300000</v>
       </c>
-      <c r="H37" s="2">
-        <v>0</v>
-      </c>
-      <c r="I37" s="2">
-        <v>0</v>
-      </c>
-      <c r="J37" s="2">
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="I37" s="1">
+        <v>0</v>
+      </c>
+      <c r="J37" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C38" t="s">
+      <c r="B38" s="1"/>
+      <c r="C38" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E38" t="s">
+      <c r="D38" s="1"/>
+      <c r="E38" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G38" s="2">
-        <v>0</v>
-      </c>
-      <c r="H38" s="2">
+      <c r="F38" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
         <v>1500000</v>
       </c>
-      <c r="I38" s="2">
+      <c r="I38" s="1">
         <v>1500000</v>
       </c>
       <c r="J38" s="2">
@@ -2339,48 +2898,50 @@
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="A39" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C39" t="s">
+      <c r="B39" s="1"/>
+      <c r="C39" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F39" t="s">
-        <v>12</v>
-      </c>
-      <c r="G39" s="2">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2">
-        <v>0</v>
-      </c>
-      <c r="I39" s="2">
-        <v>0</v>
-      </c>
-      <c r="J39" s="2">
+      <c r="F39" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="1">
         <v>10000000</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="A40" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C40" t="s">
+      <c r="B40" s="1"/>
+      <c r="C40" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G40" s="2">
@@ -2397,48 +2958,50 @@
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="A41" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C41" t="s">
+      <c r="B41" s="1"/>
+      <c r="C41" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F41" t="s">
-        <v>35</v>
-      </c>
-      <c r="G41" s="2">
-        <v>0</v>
-      </c>
-      <c r="H41" s="2">
-        <v>0</v>
-      </c>
-      <c r="I41" s="2">
-        <v>0</v>
-      </c>
-      <c r="J41" s="2">
+      <c r="F41" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1">
         <v>10000000</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="A42" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C42" t="s">
+      <c r="B42" s="1"/>
+      <c r="C42" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G42" s="2">
@@ -2455,19 +3018,20 @@
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="A43" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C43" t="s">
+      <c r="B43" s="1"/>
+      <c r="C43" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G43" s="2">
@@ -2484,19 +3048,20 @@
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="A44" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C44" t="s">
+      <c r="B44" s="1"/>
+      <c r="C44" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G44" s="2">
@@ -2513,19 +3078,20 @@
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="A45" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C45" t="s">
+      <c r="B45" s="1"/>
+      <c r="C45" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G45" s="2">
@@ -2542,19 +3108,20 @@
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="A46" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C46" t="s">
+      <c r="B46" s="1"/>
+      <c r="C46" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G46" s="2">
@@ -2571,19 +3138,20 @@
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="A47" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C47" t="s">
+      <c r="B47" s="1"/>
+      <c r="C47" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G47" s="2">
@@ -2600,19 +3168,20 @@
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="A48" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C48" t="s">
+      <c r="B48" s="1"/>
+      <c r="C48" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G48" s="2">
@@ -2629,19 +3198,20 @@
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="A49" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C49" t="s">
+      <c r="B49" s="1"/>
+      <c r="C49" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G49" s="2">
@@ -2658,19 +3228,20 @@
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="A50" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C50" t="s">
+      <c r="B50" s="1"/>
+      <c r="C50" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G50" s="2">
@@ -2687,19 +3258,20 @@
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="A51" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C51" t="s">
+      <c r="B51" s="1"/>
+      <c r="C51" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G51" s="2">
@@ -2716,19 +3288,20 @@
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="A52" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C52" t="s">
+      <c r="B52" s="1"/>
+      <c r="C52" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G52" s="2">
@@ -2745,19 +3318,20 @@
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="A53" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C53" t="s">
+      <c r="B53" s="1"/>
+      <c r="C53" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G53" s="2">
@@ -2774,19 +3348,20 @@
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="A54" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C54" t="s">
+      <c r="B54" s="1"/>
+      <c r="C54" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G54" s="2">
@@ -2803,19 +3378,20 @@
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="A55" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C55" t="s">
+      <c r="B55" s="1"/>
+      <c r="C55" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F55" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G55" s="2">
@@ -2832,19 +3408,20 @@
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="A56" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C56" t="s">
+      <c r="B56" s="1"/>
+      <c r="C56" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F56" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G56" s="2">
@@ -2861,19 +3438,20 @@
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="A57" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C57" t="s">
+      <c r="B57" s="1"/>
+      <c r="C57" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F57" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G57" s="2">
@@ -2890,19 +3468,20 @@
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="A58" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C58" t="s">
+      <c r="B58" s="1"/>
+      <c r="C58" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F58" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G58" s="2">
@@ -2919,19 +3498,20 @@
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="A59" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C59" t="s">
+      <c r="B59" s="1"/>
+      <c r="C59" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F59" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G59" s="2">
@@ -2948,48 +3528,50 @@
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="A60" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C60" t="s">
+      <c r="B60" s="1"/>
+      <c r="C60" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F60" t="s">
-        <v>12</v>
-      </c>
-      <c r="G60" s="2">
-        <v>0</v>
-      </c>
-      <c r="H60" s="2">
-        <v>0</v>
-      </c>
-      <c r="I60" s="2">
-        <v>0</v>
-      </c>
-      <c r="J60" s="2">
+      <c r="F60" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+      <c r="I60" s="1">
+        <v>0</v>
+      </c>
+      <c r="J60" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="A61" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C61" t="s">
+      <c r="B61" s="1"/>
+      <c r="C61" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F61" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G61" s="2">
@@ -3006,48 +3588,50 @@
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="A62" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C62" t="s">
+      <c r="B62" s="1"/>
+      <c r="C62" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F62" t="s">
-        <v>12</v>
-      </c>
-      <c r="G62" s="2">
-        <v>0</v>
-      </c>
-      <c r="H62" s="2">
-        <v>0</v>
-      </c>
-      <c r="I62" s="2">
-        <v>0</v>
-      </c>
-      <c r="J62" s="2">
+      <c r="F62" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0</v>
+      </c>
+      <c r="I62" s="1">
+        <v>0</v>
+      </c>
+      <c r="J62" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="A63" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C63" t="s">
+      <c r="B63" s="1"/>
+      <c r="C63" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F63" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G63" s="2">
@@ -3064,135 +3648,140 @@
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="A64" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C64" t="s">
+      <c r="B64" s="1"/>
+      <c r="C64" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F64" t="s">
-        <v>12</v>
-      </c>
-      <c r="G64" s="2">
-        <v>0</v>
-      </c>
-      <c r="H64" s="2">
-        <v>0</v>
-      </c>
-      <c r="I64" s="2">
-        <v>0</v>
-      </c>
-      <c r="J64" s="2">
+      <c r="F64" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0</v>
+      </c>
+      <c r="H64" s="1">
+        <v>0</v>
+      </c>
+      <c r="I64" s="1">
+        <v>0</v>
+      </c>
+      <c r="J64" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="A65" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C65" t="s">
+      <c r="B65" s="1"/>
+      <c r="C65" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E65" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F65" t="s">
-        <v>12</v>
-      </c>
-      <c r="G65" s="2">
-        <v>0</v>
-      </c>
-      <c r="H65" s="2">
-        <v>0</v>
-      </c>
-      <c r="I65" s="2">
-        <v>0</v>
-      </c>
-      <c r="J65" s="2">
+      <c r="F65" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0</v>
+      </c>
+      <c r="H65" s="1">
+        <v>0</v>
+      </c>
+      <c r="I65" s="1">
+        <v>0</v>
+      </c>
+      <c r="J65" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="A66" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C66" t="s">
+      <c r="B66" s="1"/>
+      <c r="C66" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F66" t="s">
-        <v>12</v>
-      </c>
-      <c r="G66" s="2">
-        <v>0</v>
-      </c>
-      <c r="H66" s="2">
-        <v>0</v>
-      </c>
-      <c r="I66" s="2">
-        <v>0</v>
-      </c>
-      <c r="J66" s="2">
+      <c r="F66" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0</v>
+      </c>
+      <c r="H66" s="1">
+        <v>0</v>
+      </c>
+      <c r="I66" s="1">
+        <v>0</v>
+      </c>
+      <c r="J66" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="A67" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C67" t="s">
+      <c r="B67" s="1"/>
+      <c r="C67" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E67" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F67" t="s">
-        <v>12</v>
-      </c>
-      <c r="G67" s="2">
-        <v>0</v>
-      </c>
-      <c r="H67" s="2">
-        <v>0</v>
-      </c>
-      <c r="I67" s="2">
-        <v>0</v>
-      </c>
-      <c r="J67" s="2">
+      <c r="F67" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0</v>
+      </c>
+      <c r="H67" s="1">
+        <v>0</v>
+      </c>
+      <c r="I67" s="1">
+        <v>0</v>
+      </c>
+      <c r="J67" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="A68" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C68" t="s">
+      <c r="B68" s="1"/>
+      <c r="C68" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E68" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="F68" t="s">
+      <c r="F68" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G68" s="2">
@@ -3209,48 +3798,50 @@
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="A69" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C69" t="s">
+      <c r="B69" s="1"/>
+      <c r="C69" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E69" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F69" t="s">
-        <v>12</v>
-      </c>
-      <c r="G69" s="2">
-        <v>0</v>
-      </c>
-      <c r="H69" s="2">
-        <v>0</v>
-      </c>
-      <c r="I69" s="2">
-        <v>0</v>
-      </c>
-      <c r="J69" s="2">
+      <c r="F69" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0</v>
+      </c>
+      <c r="H69" s="1">
+        <v>0</v>
+      </c>
+      <c r="I69" s="1">
+        <v>0</v>
+      </c>
+      <c r="J69" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="A70" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C70" t="s">
+      <c r="B70" s="1"/>
+      <c r="C70" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E70" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F70" t="s">
+      <c r="F70" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G70" s="2">
@@ -3267,19 +3858,20 @@
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="A71" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C71" t="s">
+      <c r="B71" s="1"/>
+      <c r="C71" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E71" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F71" t="s">
+      <c r="F71" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G71" s="2">
@@ -3296,19 +3888,20 @@
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="A72" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C72" t="s">
+      <c r="B72" s="1"/>
+      <c r="C72" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E72" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F72" t="s">
+      <c r="F72" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G72" s="2">
@@ -3325,19 +3918,20 @@
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="A73" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C73" t="s">
+      <c r="B73" s="1"/>
+      <c r="C73" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E73" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="F73" t="s">
+      <c r="F73" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G73" s="2">
@@ -3354,19 +3948,20 @@
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="A74" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C74" t="s">
+      <c r="B74" s="1"/>
+      <c r="C74" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E74" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F74" t="s">
+      <c r="F74" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G74" s="2">
@@ -3383,19 +3978,20 @@
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="A75" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C75" t="s">
+      <c r="B75" s="1"/>
+      <c r="C75" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E75" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="F75" t="s">
+      <c r="F75" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G75" s="2">
@@ -3412,77 +4008,80 @@
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="A76" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C76" t="s">
+      <c r="B76" s="1"/>
+      <c r="C76" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E76" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="F76" t="s">
-        <v>12</v>
-      </c>
-      <c r="G76" s="2">
-        <v>0</v>
-      </c>
-      <c r="H76" s="2">
-        <v>0</v>
-      </c>
-      <c r="I76" s="2">
-        <v>0</v>
-      </c>
-      <c r="J76" s="2">
+      <c r="F76" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0</v>
+      </c>
+      <c r="H76" s="1">
+        <v>0</v>
+      </c>
+      <c r="I76" s="1">
+        <v>0</v>
+      </c>
+      <c r="J76" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="A77" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C77" t="s">
+      <c r="B77" s="1"/>
+      <c r="C77" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D77" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E77" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="F77" t="s">
-        <v>12</v>
-      </c>
-      <c r="G77" s="2">
-        <v>0</v>
-      </c>
-      <c r="H77" s="2">
-        <v>0</v>
-      </c>
-      <c r="I77" s="2">
-        <v>0</v>
-      </c>
-      <c r="J77" s="2">
+      <c r="F77" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0</v>
+      </c>
+      <c r="H77" s="1">
+        <v>0</v>
+      </c>
+      <c r="I77" s="1">
+        <v>0</v>
+      </c>
+      <c r="J77" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="A78" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C78" t="s">
+      <c r="B78" s="1"/>
+      <c r="C78" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D78" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E78" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="F78" t="s">
+      <c r="F78" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G78" s="2">
@@ -3499,19 +4098,20 @@
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="A79" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C79" t="s">
+      <c r="B79" s="1"/>
+      <c r="C79" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D79" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E79" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="F79" t="s">
+      <c r="F79" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G79" s="2">
@@ -3528,19 +4128,20 @@
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="A80" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C80" t="s">
+      <c r="B80" s="1"/>
+      <c r="C80" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E80" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F80" t="s">
+      <c r="F80" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G80" s="2">
@@ -3557,19 +4158,20 @@
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="A81" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C81" t="s">
+      <c r="B81" s="1"/>
+      <c r="C81" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D81" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E81" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F81" t="s">
+      <c r="F81" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G81" s="2">
@@ -3586,19 +4188,20 @@
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="A82" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C82" t="s">
+      <c r="B82" s="1"/>
+      <c r="C82" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E82" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F82" t="s">
+      <c r="F82" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G82" s="2">
@@ -3615,19 +4218,20 @@
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="A83" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C83" t="s">
+      <c r="B83" s="1"/>
+      <c r="C83" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E83" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F83" t="s">
+      <c r="F83" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G83" s="2">
@@ -3644,77 +4248,80 @@
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="A84" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C84" t="s">
+      <c r="B84" s="1"/>
+      <c r="C84" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D84" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E84" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="F84" t="s">
-        <v>12</v>
-      </c>
-      <c r="G84" s="2">
-        <v>0</v>
-      </c>
-      <c r="H84" s="2">
-        <v>0</v>
-      </c>
-      <c r="I84" s="2">
-        <v>0</v>
-      </c>
-      <c r="J84" s="2">
+      <c r="F84" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G84" s="1">
+        <v>0</v>
+      </c>
+      <c r="H84" s="1">
+        <v>0</v>
+      </c>
+      <c r="I84" s="1">
+        <v>0</v>
+      </c>
+      <c r="J84" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="A85" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C85" t="s">
+      <c r="B85" s="1"/>
+      <c r="C85" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E85" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="F85" t="s">
-        <v>12</v>
-      </c>
-      <c r="G85" s="2">
-        <v>0</v>
-      </c>
-      <c r="H85" s="2">
-        <v>0</v>
-      </c>
-      <c r="I85" s="2">
-        <v>0</v>
-      </c>
-      <c r="J85" s="2">
+      <c r="F85" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0</v>
+      </c>
+      <c r="H85" s="1">
+        <v>0</v>
+      </c>
+      <c r="I85" s="1">
+        <v>0</v>
+      </c>
+      <c r="J85" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="A86" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C86" t="s">
+      <c r="B86" s="1"/>
+      <c r="C86" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E86" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F86" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G86" s="2">
@@ -3731,19 +4338,20 @@
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="A87" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C87" t="s">
+      <c r="B87" s="1"/>
+      <c r="C87" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D87" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E87" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F87" t="s">
+      <c r="F87" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G87" s="2">
@@ -3760,19 +4368,20 @@
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="A88" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C88" t="s">
+      <c r="B88" s="1"/>
+      <c r="C88" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E88" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F88" t="s">
+      <c r="F88" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G88" s="2">
@@ -3789,19 +4398,20 @@
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="A89" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C89" t="s">
+      <c r="B89" s="1"/>
+      <c r="C89" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E89" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F89" t="s">
+      <c r="F89" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G89" s="2">
@@ -3818,19 +4428,20 @@
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="A90" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C90" t="s">
+      <c r="B90" s="1"/>
+      <c r="C90" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D90" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E90" t="s">
+      <c r="E90" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F90" t="s">
+      <c r="F90" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G90" s="2">
@@ -3847,19 +4458,20 @@
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="A91" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C91" t="s">
+      <c r="B91" s="1"/>
+      <c r="C91" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D91" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E91" t="s">
+      <c r="E91" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F91" t="s">
+      <c r="F91" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G91" s="2">
@@ -3876,19 +4488,20 @@
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+      <c r="A92" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C92" t="s">
+      <c r="B92" s="1"/>
+      <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D92" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E92" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F92" t="s">
+      <c r="F92" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G92" s="2">
@@ -3905,19 +4518,20 @@
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+      <c r="A93" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C93" t="s">
+      <c r="B93" s="1"/>
+      <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D93" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E93" t="s">
+      <c r="E93" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F93" t="s">
+      <c r="F93" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G93" s="2">
@@ -3934,19 +4548,20 @@
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+      <c r="A94" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C94" t="s">
+      <c r="B94" s="1"/>
+      <c r="C94" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D94" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E94" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F94" t="s">
+      <c r="F94" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G94" s="2">
@@ -3963,19 +4578,20 @@
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
+      <c r="A95" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C95" t="s">
+      <c r="B95" s="1"/>
+      <c r="C95" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D95" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E95" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F95" t="s">
+      <c r="F95" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G95" s="2">
@@ -3992,19 +4608,20 @@
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+      <c r="A96" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C96" t="s">
+      <c r="B96" s="1"/>
+      <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D96" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E96" t="s">
+      <c r="E96" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F96" t="s">
+      <c r="F96" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G96" s="2">
@@ -4021,19 +4638,20 @@
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+      <c r="A97" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C97" t="s">
+      <c r="B97" s="1"/>
+      <c r="C97" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D97" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E97" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F97" t="s">
+      <c r="F97" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G97" s="2">
@@ -4050,19 +4668,20 @@
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+      <c r="A98" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C98" t="s">
+      <c r="B98" s="1"/>
+      <c r="C98" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E98" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F98" t="s">
+      <c r="F98" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G98" s="2">
@@ -4079,19 +4698,20 @@
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+      <c r="A99" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C99" t="s">
+      <c r="B99" s="1"/>
+      <c r="C99" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D99" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E99" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F99" t="s">
+      <c r="F99" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G99" s="2">
@@ -4108,19 +4728,20 @@
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+      <c r="A100" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C100" t="s">
+      <c r="B100" s="1"/>
+      <c r="C100" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D100" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E100" t="s">
+      <c r="E100" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F100" t="s">
+      <c r="F100" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G100" s="2">
@@ -4137,19 +4758,20 @@
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="A101" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C101" t="s">
+      <c r="B101" s="1"/>
+      <c r="C101" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E101" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F101" t="s">
+      <c r="F101" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G101" s="2">
@@ -4166,19 +4788,20 @@
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+      <c r="A102" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C102" t="s">
+      <c r="B102" s="1"/>
+      <c r="C102" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E102" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F102" t="s">
+      <c r="F102" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G102" s="2">
@@ -4195,48 +4818,50 @@
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+      <c r="A103" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C103" t="s">
+      <c r="B103" s="1"/>
+      <c r="C103" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E103" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F103" t="s">
-        <v>35</v>
-      </c>
-      <c r="G103" s="2">
-        <v>0</v>
-      </c>
-      <c r="H103" s="2">
-        <v>0</v>
-      </c>
-      <c r="I103" s="2">
-        <v>0</v>
-      </c>
-      <c r="J103" s="2">
+      <c r="F103" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G103" s="1">
+        <v>0</v>
+      </c>
+      <c r="H103" s="1">
+        <v>0</v>
+      </c>
+      <c r="I103" s="1">
+        <v>0</v>
+      </c>
+      <c r="J103" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+      <c r="A104" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C104" t="s">
+      <c r="B104" s="1"/>
+      <c r="C104" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D104" t="s">
+      <c r="D104" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E104" t="s">
+      <c r="E104" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F104" t="s">
+      <c r="F104" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G104" s="2">
@@ -4253,48 +4878,50 @@
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+      <c r="A105" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C105" t="s">
+      <c r="B105" s="1"/>
+      <c r="C105" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D105" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E105" t="s">
+      <c r="E105" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F105" t="s">
-        <v>35</v>
-      </c>
-      <c r="G105" s="2">
-        <v>0</v>
-      </c>
-      <c r="H105" s="2">
-        <v>0</v>
-      </c>
-      <c r="I105" s="2">
-        <v>0</v>
-      </c>
-      <c r="J105" s="2">
+      <c r="F105" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G105" s="1">
+        <v>0</v>
+      </c>
+      <c r="H105" s="1">
+        <v>0</v>
+      </c>
+      <c r="I105" s="1">
+        <v>0</v>
+      </c>
+      <c r="J105" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+      <c r="A106" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C106" t="s">
+      <c r="B106" s="1"/>
+      <c r="C106" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D106" t="s">
+      <c r="D106" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E106" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="F106" t="s">
+      <c r="F106" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G106" s="2">
@@ -4311,135 +4938,140 @@
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+      <c r="A107" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C107" t="s">
+      <c r="B107" s="1"/>
+      <c r="C107" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D107" t="s">
+      <c r="D107" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E107" t="s">
+      <c r="E107" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F107" t="s">
-        <v>35</v>
-      </c>
-      <c r="G107" s="2">
-        <v>0</v>
-      </c>
-      <c r="H107" s="2">
-        <v>0</v>
-      </c>
-      <c r="I107" s="2">
-        <v>0</v>
-      </c>
-      <c r="J107" s="2">
+      <c r="F107" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G107" s="1">
+        <v>0</v>
+      </c>
+      <c r="H107" s="1">
+        <v>0</v>
+      </c>
+      <c r="I107" s="1">
+        <v>0</v>
+      </c>
+      <c r="J107" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+      <c r="A108" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C108" t="s">
+      <c r="B108" s="1"/>
+      <c r="C108" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D108" t="s">
+      <c r="D108" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E108" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F108" t="s">
-        <v>35</v>
-      </c>
-      <c r="G108" s="2">
-        <v>0</v>
-      </c>
-      <c r="H108" s="2">
-        <v>0</v>
-      </c>
-      <c r="I108" s="2">
-        <v>0</v>
-      </c>
-      <c r="J108" s="2">
+      <c r="F108" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G108" s="1">
+        <v>0</v>
+      </c>
+      <c r="H108" s="1">
+        <v>0</v>
+      </c>
+      <c r="I108" s="1">
+        <v>0</v>
+      </c>
+      <c r="J108" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+      <c r="A109" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C109" t="s">
+      <c r="B109" s="1"/>
+      <c r="C109" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D109" t="s">
+      <c r="D109" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E109" t="s">
+      <c r="E109" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F109" t="s">
-        <v>35</v>
-      </c>
-      <c r="G109" s="2">
-        <v>0</v>
-      </c>
-      <c r="H109" s="2">
-        <v>0</v>
-      </c>
-      <c r="I109" s="2">
-        <v>0</v>
-      </c>
-      <c r="J109" s="2">
+      <c r="F109" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G109" s="1">
+        <v>0</v>
+      </c>
+      <c r="H109" s="1">
+        <v>0</v>
+      </c>
+      <c r="I109" s="1">
+        <v>0</v>
+      </c>
+      <c r="J109" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="A110" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C110" t="s">
+      <c r="B110" s="1"/>
+      <c r="C110" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D110" t="s">
+      <c r="D110" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E110" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F110" t="s">
-        <v>35</v>
-      </c>
-      <c r="G110" s="2">
-        <v>0</v>
-      </c>
-      <c r="H110" s="2">
-        <v>0</v>
-      </c>
-      <c r="I110" s="2">
-        <v>0</v>
-      </c>
-      <c r="J110" s="2">
+      <c r="F110" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G110" s="1">
+        <v>0</v>
+      </c>
+      <c r="H110" s="1">
+        <v>0</v>
+      </c>
+      <c r="I110" s="1">
+        <v>0</v>
+      </c>
+      <c r="J110" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+      <c r="A111" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C111" t="s">
+      <c r="B111" s="1"/>
+      <c r="C111" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D111" t="s">
+      <c r="D111" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E111" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="F111" t="s">
+      <c r="F111" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G111" s="2">
@@ -4456,48 +5088,50 @@
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+      <c r="A112" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C112" t="s">
+      <c r="B112" s="1"/>
+      <c r="C112" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D112" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E112" t="s">
+      <c r="E112" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F112" t="s">
-        <v>35</v>
-      </c>
-      <c r="G112" s="2">
-        <v>0</v>
-      </c>
-      <c r="H112" s="2">
-        <v>0</v>
-      </c>
-      <c r="I112" s="2">
-        <v>0</v>
-      </c>
-      <c r="J112" s="2">
+      <c r="F112" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G112" s="1">
+        <v>0</v>
+      </c>
+      <c r="H112" s="1">
+        <v>0</v>
+      </c>
+      <c r="I112" s="1">
+        <v>0</v>
+      </c>
+      <c r="J112" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+      <c r="A113" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C113" t="s">
+      <c r="B113" s="1"/>
+      <c r="C113" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D113" t="s">
+      <c r="D113" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E113" t="s">
+      <c r="E113" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F113" t="s">
+      <c r="F113" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G113" s="2">
@@ -4514,19 +5148,20 @@
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
+      <c r="A114" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C114" t="s">
+      <c r="B114" s="1"/>
+      <c r="C114" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D114" t="s">
+      <c r="D114" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E114" t="s">
+      <c r="E114" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F114" t="s">
+      <c r="F114" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G114" s="2">
@@ -4543,19 +5178,20 @@
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
+      <c r="A115" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C115" t="s">
+      <c r="B115" s="1"/>
+      <c r="C115" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D115" t="s">
+      <c r="D115" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E115" t="s">
+      <c r="E115" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F115" t="s">
+      <c r="F115" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G115" s="2">
@@ -4572,19 +5208,20 @@
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+      <c r="A116" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C116" t="s">
+      <c r="B116" s="1"/>
+      <c r="C116" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D116" t="s">
+      <c r="D116" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E116" t="s">
+      <c r="E116" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="F116" t="s">
+      <c r="F116" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G116" s="2">
@@ -4601,19 +5238,20 @@
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+      <c r="A117" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C117" t="s">
+      <c r="B117" s="1"/>
+      <c r="C117" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D117" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E117" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F117" t="s">
+      <c r="F117" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G117" s="2">
@@ -4630,19 +5268,20 @@
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+      <c r="A118" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C118" t="s">
+      <c r="B118" s="1"/>
+      <c r="C118" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D118" t="s">
+      <c r="D118" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E118" t="s">
+      <c r="E118" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="F118" t="s">
+      <c r="F118" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G118" s="2">
@@ -4659,77 +5298,80 @@
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
+      <c r="A119" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C119" t="s">
+      <c r="B119" s="1"/>
+      <c r="C119" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D119" t="s">
+      <c r="D119" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E119" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="F119" t="s">
-        <v>35</v>
-      </c>
-      <c r="G119" s="2">
-        <v>0</v>
-      </c>
-      <c r="H119" s="2">
-        <v>0</v>
-      </c>
-      <c r="I119" s="2">
-        <v>0</v>
-      </c>
-      <c r="J119" s="2">
+      <c r="F119" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G119" s="1">
+        <v>0</v>
+      </c>
+      <c r="H119" s="1">
+        <v>0</v>
+      </c>
+      <c r="I119" s="1">
+        <v>0</v>
+      </c>
+      <c r="J119" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
+      <c r="A120" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C120" t="s">
+      <c r="B120" s="1"/>
+      <c r="C120" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D120" t="s">
+      <c r="D120" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E120" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="F120" t="s">
-        <v>35</v>
-      </c>
-      <c r="G120" s="2">
-        <v>0</v>
-      </c>
-      <c r="H120" s="2">
-        <v>0</v>
-      </c>
-      <c r="I120" s="2">
-        <v>0</v>
-      </c>
-      <c r="J120" s="2">
+      <c r="F120" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G120" s="1">
+        <v>0</v>
+      </c>
+      <c r="H120" s="1">
+        <v>0</v>
+      </c>
+      <c r="I120" s="1">
+        <v>0</v>
+      </c>
+      <c r="J120" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
+      <c r="A121" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C121" t="s">
+      <c r="B121" s="1"/>
+      <c r="C121" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D121" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E121" t="s">
+      <c r="E121" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="F121" t="s">
+      <c r="F121" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G121" s="2">
@@ -4746,19 +5388,20 @@
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
+      <c r="A122" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C122" t="s">
+      <c r="B122" s="1"/>
+      <c r="C122" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D122" t="s">
+      <c r="D122" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E122" t="s">
+      <c r="E122" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="F122" t="s">
+      <c r="F122" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G122" s="2">
@@ -4775,19 +5418,20 @@
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+      <c r="A123" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C123" t="s">
+      <c r="B123" s="1"/>
+      <c r="C123" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D123" t="s">
+      <c r="D123" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E123" t="s">
+      <c r="E123" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F123" t="s">
+      <c r="F123" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G123" s="2">
@@ -4804,19 +5448,20 @@
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
+      <c r="A124" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C124" t="s">
+      <c r="B124" s="1"/>
+      <c r="C124" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D124" t="s">
+      <c r="D124" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E124" t="s">
+      <c r="E124" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F124" t="s">
+      <c r="F124" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G124" s="2">
@@ -4833,19 +5478,20 @@
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+      <c r="A125" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C125" t="s">
+      <c r="B125" s="1"/>
+      <c r="C125" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D125" t="s">
+      <c r="D125" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E125" t="s">
+      <c r="E125" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F125" t="s">
+      <c r="F125" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G125" s="2">
@@ -4862,19 +5508,20 @@
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
+      <c r="A126" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C126" t="s">
+      <c r="B126" s="1"/>
+      <c r="C126" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D126" t="s">
+      <c r="D126" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E126" t="s">
+      <c r="E126" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F126" t="s">
+      <c r="F126" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G126" s="2">
@@ -4891,77 +5538,80 @@
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
+      <c r="A127" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C127" t="s">
+      <c r="B127" s="1"/>
+      <c r="C127" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D127" t="s">
+      <c r="D127" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E127" t="s">
+      <c r="E127" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="F127" t="s">
-        <v>35</v>
-      </c>
-      <c r="G127" s="2">
-        <v>0</v>
-      </c>
-      <c r="H127" s="2">
-        <v>0</v>
-      </c>
-      <c r="I127" s="2">
-        <v>0</v>
-      </c>
-      <c r="J127" s="2">
+      <c r="F127" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G127" s="1">
+        <v>0</v>
+      </c>
+      <c r="H127" s="1">
+        <v>0</v>
+      </c>
+      <c r="I127" s="1">
+        <v>0</v>
+      </c>
+      <c r="J127" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
+      <c r="A128" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C128" t="s">
+      <c r="B128" s="1"/>
+      <c r="C128" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D128" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E128" t="s">
+      <c r="E128" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="F128" t="s">
-        <v>35</v>
-      </c>
-      <c r="G128" s="2">
-        <v>0</v>
-      </c>
-      <c r="H128" s="2">
-        <v>0</v>
-      </c>
-      <c r="I128" s="2">
-        <v>0</v>
-      </c>
-      <c r="J128" s="2">
+      <c r="F128" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G128" s="1">
+        <v>0</v>
+      </c>
+      <c r="H128" s="1">
+        <v>0</v>
+      </c>
+      <c r="I128" s="1">
+        <v>0</v>
+      </c>
+      <c r="J128" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+      <c r="A129" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C129" t="s">
+      <c r="B129" s="1"/>
+      <c r="C129" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D129" t="s">
+      <c r="D129" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E129" t="s">
+      <c r="E129" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F129" t="s">
+      <c r="F129" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G129" s="2">
@@ -4978,19 +5628,20 @@
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
+      <c r="A130" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C130" t="s">
+      <c r="B130" s="1"/>
+      <c r="C130" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D130" t="s">
+      <c r="D130" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E130" t="s">
+      <c r="E130" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F130" t="s">
+      <c r="F130" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G130" s="2">
@@ -5007,60 +5658,61 @@
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+      <c r="A131" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C131" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="E131" t="s">
+      <c r="D131" s="1"/>
+      <c r="E131" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F131" t="s">
-        <v>35</v>
-      </c>
-      <c r="G131" s="2">
-        <v>0</v>
-      </c>
-      <c r="H131" s="2">
-        <v>0</v>
-      </c>
-      <c r="I131" s="2">
-        <v>0</v>
-      </c>
-      <c r="J131" s="2">
+      <c r="F131" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G131" s="1">
+        <v>0</v>
+      </c>
+      <c r="H131" s="1">
+        <v>0</v>
+      </c>
+      <c r="I131" s="1">
+        <v>0</v>
+      </c>
+      <c r="J131" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
+      <c r="A132" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C132" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D132" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E132" t="s">
+      <c r="E132" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="F132" t="s">
-        <v>35</v>
-      </c>
-      <c r="G132" s="2">
+      <c r="F132" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G132" s="1">
         <v>0</v>
       </c>
       <c r="H132" s="2">
         <v>145345427</v>
       </c>
-      <c r="I132" s="2">
+      <c r="I132" s="1">
         <v>0</v>
       </c>
       <c r="J132" s="2">
@@ -5068,54 +5720,54 @@
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
+      <c r="A133" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C133" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D133" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E133" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="F133" t="s">
-        <v>35</v>
-      </c>
-      <c r="G133" s="2">
-        <v>0</v>
-      </c>
-      <c r="H133" s="2">
-        <v>0</v>
-      </c>
-      <c r="I133" s="2">
-        <v>0</v>
-      </c>
-      <c r="J133" s="2">
+      <c r="F133" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G133" s="1">
+        <v>0</v>
+      </c>
+      <c r="H133" s="1">
+        <v>0</v>
+      </c>
+      <c r="I133" s="1">
+        <v>0</v>
+      </c>
+      <c r="J133" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
+      <c r="A134" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C134" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D134" t="s">
+      <c r="D134" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E134" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F134" t="s">
+      <c r="F134" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G134" s="2">
@@ -5132,25 +5784,25 @@
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
+      <c r="A135" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C135" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D135" t="s">
+      <c r="D135" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E135" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F135" t="s">
-        <v>35</v>
-      </c>
-      <c r="G135" s="2">
+      <c r="F135" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G135" s="1">
         <v>0</v>
       </c>
       <c r="H135" s="2">
@@ -5164,22 +5816,22 @@
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
+      <c r="A136" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C136" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D136" t="s">
+      <c r="D136" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="E136" t="s">
+      <c r="E136" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F136" t="s">
+      <c r="F136" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G136" s="2">
@@ -5196,54 +5848,54 @@
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
+      <c r="A137" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C137" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D137" t="s">
+      <c r="D137" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E137" t="s">
+      <c r="E137" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="F137" t="s">
-        <v>35</v>
-      </c>
-      <c r="G137" s="2">
-        <v>0</v>
-      </c>
-      <c r="H137" s="2">
-        <v>0</v>
-      </c>
-      <c r="I137" s="2">
-        <v>0</v>
-      </c>
-      <c r="J137" s="2">
+      <c r="F137" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G137" s="1">
+        <v>0</v>
+      </c>
+      <c r="H137" s="1">
+        <v>0</v>
+      </c>
+      <c r="I137" s="1">
+        <v>0</v>
+      </c>
+      <c r="J137" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
+      <c r="A138" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C138" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D138" t="s">
+      <c r="D138" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E138" t="s">
+      <c r="E138" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F138" t="s">
+      <c r="F138" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G138" s="2">
@@ -5260,89 +5912,89 @@
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
+      <c r="A139" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C139" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D139" t="s">
+      <c r="D139" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E139" t="s">
+      <c r="E139" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="F139" t="s">
+      <c r="F139" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="G139" s="2">
-        <v>0</v>
-      </c>
-      <c r="H139" s="2">
-        <v>0</v>
-      </c>
-      <c r="I139" s="2">
-        <v>0</v>
-      </c>
-      <c r="J139" s="2">
+      <c r="G139" s="1">
+        <v>0</v>
+      </c>
+      <c r="H139" s="1">
+        <v>0</v>
+      </c>
+      <c r="I139" s="1">
+        <v>0</v>
+      </c>
+      <c r="J139" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
+      <c r="A140" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C140" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D140" t="s">
+      <c r="D140" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="E140" t="s">
+      <c r="E140" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="F140" t="s">
+      <c r="F140" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="G140" s="2">
-        <v>0</v>
-      </c>
-      <c r="H140" s="2">
-        <v>0</v>
-      </c>
-      <c r="I140" s="2">
-        <v>0</v>
-      </c>
-      <c r="J140" s="2">
+      <c r="G140" s="1">
+        <v>0</v>
+      </c>
+      <c r="H140" s="1">
+        <v>0</v>
+      </c>
+      <c r="I140" s="1">
+        <v>0</v>
+      </c>
+      <c r="J140" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
+      <c r="A141" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C141" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D141" t="s">
+      <c r="D141" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E141" t="s">
+      <c r="E141" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F141" t="s">
+      <c r="F141" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="G141" s="2">
+      <c r="G141" s="1">
         <v>0</v>
       </c>
       <c r="H141" s="2">
@@ -5351,36 +6003,36 @@
       <c r="I141" s="2">
         <v>13020000</v>
       </c>
-      <c r="J141" s="2">
+      <c r="J141" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
+      <c r="A142" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C142" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D142" t="s">
+      <c r="D142" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E142" t="s">
+      <c r="E142" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="F142" t="s">
+      <c r="F142" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="G142" s="2">
-        <v>0</v>
-      </c>
-      <c r="H142" s="2">
-        <v>0</v>
-      </c>
-      <c r="I142" s="2">
+      <c r="G142" s="1">
+        <v>0</v>
+      </c>
+      <c r="H142" s="1">
+        <v>0</v>
+      </c>
+      <c r="I142" s="1">
         <v>0</v>
       </c>
       <c r="J142" s="2">
@@ -5388,25 +6040,25 @@
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
+      <c r="A143" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C143" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D143" t="s">
+      <c r="D143" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E143" t="s">
+      <c r="E143" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F143" t="s">
+      <c r="F143" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="G143" s="2">
+      <c r="G143" s="1">
         <v>0</v>
       </c>
       <c r="H143" s="2">
@@ -5420,118 +6072,118 @@
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
+      <c r="A144" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C144" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D144" t="s">
+      <c r="D144" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E144" t="s">
+      <c r="E144" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="F144" t="s">
+      <c r="F144" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="G144" s="2">
-        <v>0</v>
-      </c>
-      <c r="H144" s="2">
-        <v>0</v>
-      </c>
-      <c r="I144" s="2">
-        <v>0</v>
-      </c>
-      <c r="J144" s="2">
+      <c r="G144" s="1">
+        <v>0</v>
+      </c>
+      <c r="H144" s="1">
+        <v>0</v>
+      </c>
+      <c r="I144" s="1">
+        <v>0</v>
+      </c>
+      <c r="J144" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
+      <c r="A145" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C145" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D145" t="s">
+      <c r="D145" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E145" t="s">
+      <c r="E145" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F145" t="s">
+      <c r="F145" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="G145" s="2">
-        <v>0</v>
-      </c>
-      <c r="H145" s="2">
-        <v>0</v>
-      </c>
-      <c r="I145" s="2">
-        <v>0</v>
-      </c>
-      <c r="J145" s="2">
+      <c r="G145" s="1">
+        <v>0</v>
+      </c>
+      <c r="H145" s="1">
+        <v>0</v>
+      </c>
+      <c r="I145" s="1">
+        <v>0</v>
+      </c>
+      <c r="J145" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
+      <c r="A146" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C146" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D146" t="s">
+      <c r="D146" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E146" t="s">
+      <c r="E146" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="F146" t="s">
+      <c r="F146" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="G146" s="2">
-        <v>0</v>
-      </c>
-      <c r="H146" s="2">
-        <v>0</v>
-      </c>
-      <c r="I146" s="2">
-        <v>0</v>
-      </c>
-      <c r="J146" s="2">
+      <c r="G146" s="1">
+        <v>0</v>
+      </c>
+      <c r="H146" s="1">
+        <v>0</v>
+      </c>
+      <c r="I146" s="1">
+        <v>0</v>
+      </c>
+      <c r="J146" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
+      <c r="A147" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C147" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D147" t="s">
+      <c r="D147" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E147" t="s">
+      <c r="E147" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F147" t="s">
+      <c r="F147" s="1" t="s">
         <v>192</v>
       </c>
       <c r="G147" s="2">
@@ -5548,86 +6200,86 @@
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
+      <c r="A148" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C148" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D148" t="s">
+      <c r="D148" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E148" t="s">
+      <c r="E148" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="F148" t="s">
-        <v>35</v>
-      </c>
-      <c r="G148" s="2">
-        <v>0</v>
-      </c>
-      <c r="H148" s="2">
-        <v>0</v>
-      </c>
-      <c r="I148" s="2">
-        <v>0</v>
-      </c>
-      <c r="J148" s="2">
+      <c r="F148" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G148" s="1">
+        <v>0</v>
+      </c>
+      <c r="H148" s="1">
+        <v>0</v>
+      </c>
+      <c r="I148" s="1">
+        <v>0</v>
+      </c>
+      <c r="J148" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
+      <c r="A149" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C149" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D149" t="s">
+      <c r="D149" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E149" t="s">
+      <c r="E149" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F149" t="s">
-        <v>35</v>
-      </c>
-      <c r="G149" s="2">
-        <v>0</v>
-      </c>
-      <c r="H149" s="2">
-        <v>0</v>
-      </c>
-      <c r="I149" s="2">
-        <v>0</v>
-      </c>
-      <c r="J149" s="2">
+      <c r="F149" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G149" s="1">
+        <v>0</v>
+      </c>
+      <c r="H149" s="1">
+        <v>0</v>
+      </c>
+      <c r="I149" s="1">
+        <v>0</v>
+      </c>
+      <c r="J149" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
+      <c r="A150" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C150" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D150" t="s">
+      <c r="D150" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E150" t="s">
+      <c r="E150" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F150" t="s">
+      <c r="F150" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G150" s="2">
@@ -5644,28 +6296,28 @@
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
+      <c r="A151" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C151" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D151" t="s">
+      <c r="D151" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="E151" t="s">
+      <c r="E151" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F151" t="s">
+      <c r="F151" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G151" s="2">
         <v>6975000</v>
       </c>
-      <c r="H151" s="2">
+      <c r="H151" s="1">
         <v>0</v>
       </c>
       <c r="I151" s="2">
@@ -5676,22 +6328,22 @@
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
+      <c r="A152" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C152" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D152" t="s">
+      <c r="D152" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="E152" t="s">
+      <c r="E152" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="F152" t="s">
+      <c r="F152" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G152" s="2">
@@ -5703,91 +6355,91 @@
       <c r="I152" s="2">
         <v>5197500</v>
       </c>
-      <c r="J152" s="2">
+      <c r="J152" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
+      <c r="A153" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B153" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C153" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D153" t="s">
+      <c r="D153" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E153" t="s">
+      <c r="E153" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="F153" t="s">
+      <c r="F153" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G153" s="2">
         <v>16000000</v>
       </c>
-      <c r="H153" s="2">
-        <v>0</v>
-      </c>
-      <c r="I153" s="2">
-        <v>0</v>
-      </c>
-      <c r="J153" s="2">
+      <c r="H153" s="1">
+        <v>0</v>
+      </c>
+      <c r="I153" s="1">
+        <v>0</v>
+      </c>
+      <c r="J153" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
+      <c r="A154" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B154" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C154" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D154" t="s">
+      <c r="D154" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="E154" t="s">
+      <c r="E154" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F154" t="s">
-        <v>35</v>
-      </c>
-      <c r="G154" s="2">
-        <v>0</v>
-      </c>
-      <c r="H154" s="2">
-        <v>0</v>
-      </c>
-      <c r="I154" s="2">
-        <v>0</v>
-      </c>
-      <c r="J154" s="2">
+      <c r="F154" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G154" s="1">
+        <v>0</v>
+      </c>
+      <c r="H154" s="1">
+        <v>0</v>
+      </c>
+      <c r="I154" s="1">
+        <v>0</v>
+      </c>
+      <c r="J154" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
+      <c r="A155" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B155" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C155" t="s">
+      <c r="C155" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D155" t="s">
+      <c r="D155" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="E155" t="s">
+      <c r="E155" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="F155" t="s">
+      <c r="F155" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G155" s="2">
@@ -5804,22 +6456,22 @@
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
+      <c r="A156" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B156" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C156" t="s">
+      <c r="C156" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D156" t="s">
+      <c r="D156" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="E156" t="s">
+      <c r="E156" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="F156" t="s">
+      <c r="F156" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G156" s="2">
@@ -5828,65 +6480,65 @@
       <c r="H156" s="2">
         <v>5000000</v>
       </c>
-      <c r="I156" s="2">
-        <v>0</v>
-      </c>
-      <c r="J156" s="2">
+      <c r="I156" s="1">
+        <v>0</v>
+      </c>
+      <c r="J156" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
+      <c r="A157" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B157" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C157" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D157" t="s">
+      <c r="D157" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="E157" t="s">
+      <c r="E157" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F157" t="s">
-        <v>35</v>
-      </c>
-      <c r="G157" s="2">
-        <v>0</v>
-      </c>
-      <c r="H157" s="2">
-        <v>0</v>
-      </c>
-      <c r="I157" s="2">
-        <v>0</v>
-      </c>
-      <c r="J157" s="2">
+      <c r="F157" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G157" s="1">
+        <v>0</v>
+      </c>
+      <c r="H157" s="1">
+        <v>0</v>
+      </c>
+      <c r="I157" s="1">
+        <v>0</v>
+      </c>
+      <c r="J157" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
+      <c r="A158" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B158" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C158" t="s">
+      <c r="C158" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D158" t="s">
+      <c r="D158" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="E158" t="s">
+      <c r="E158" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="F158" t="s">
-        <v>35</v>
-      </c>
-      <c r="G158" s="2">
+      <c r="F158" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G158" s="3">
         <v>17289683</v>
       </c>
       <c r="H158" s="2">
@@ -5900,25 +6552,25 @@
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
+      <c r="A159" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B159" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C159" t="s">
+      <c r="C159" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D159" t="s">
+      <c r="D159" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="E159" t="s">
+      <c r="E159" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="F159" t="s">
-        <v>35</v>
-      </c>
-      <c r="G159" s="2">
+      <c r="F159" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G159" s="3">
         <v>21627032</v>
       </c>
       <c r="H159" s="2">
@@ -5932,25 +6584,25 @@
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
+      <c r="A160" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B160" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C160" t="s">
+      <c r="C160" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D160" t="s">
+      <c r="D160" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="E160" t="s">
+      <c r="E160" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="F160" t="s">
-        <v>35</v>
-      </c>
-      <c r="G160" s="2">
+      <c r="F160" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G160" s="1">
         <v>0</v>
       </c>
       <c r="H160" s="2">
@@ -5959,126 +6611,126 @@
       <c r="I160" s="2">
         <v>7750000</v>
       </c>
-      <c r="J160" s="2">
+      <c r="J160" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
+      <c r="A161" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B161" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C161" t="s">
+      <c r="C161" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D161" t="s">
+      <c r="D161" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="E161" t="s">
+      <c r="E161" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F161" t="s">
-        <v>35</v>
-      </c>
-      <c r="G161" s="2">
-        <v>0</v>
-      </c>
-      <c r="H161" s="2">
-        <v>0</v>
-      </c>
-      <c r="I161" s="2">
-        <v>0</v>
-      </c>
-      <c r="J161" s="2">
+      <c r="F161" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G161" s="1">
+        <v>0</v>
+      </c>
+      <c r="H161" s="1">
+        <v>0</v>
+      </c>
+      <c r="I161" s="1">
+        <v>0</v>
+      </c>
+      <c r="J161" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
+      <c r="A162" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B162" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C162" t="s">
+      <c r="C162" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D162" t="s">
+      <c r="D162" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E162" t="s">
+      <c r="E162" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="F162" t="s">
-        <v>35</v>
-      </c>
-      <c r="G162" s="2">
-        <v>0</v>
-      </c>
-      <c r="H162" s="2">
-        <v>0</v>
-      </c>
-      <c r="I162" s="2">
-        <v>0</v>
-      </c>
-      <c r="J162" s="2">
+      <c r="F162" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G162" s="1">
+        <v>0</v>
+      </c>
+      <c r="H162" s="1">
+        <v>0</v>
+      </c>
+      <c r="I162" s="1">
+        <v>0</v>
+      </c>
+      <c r="J162" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
+      <c r="A163" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B163" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C163" t="s">
+      <c r="C163" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D163" t="s">
+      <c r="D163" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="E163" t="s">
+      <c r="E163" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="F163" t="s">
-        <v>35</v>
-      </c>
-      <c r="G163" s="2">
-        <v>0</v>
-      </c>
-      <c r="H163" s="2">
-        <v>0</v>
-      </c>
-      <c r="I163" s="2">
-        <v>0</v>
-      </c>
-      <c r="J163" s="2">
+      <c r="F163" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G163" s="1">
+        <v>0</v>
+      </c>
+      <c r="H163" s="1">
+        <v>0</v>
+      </c>
+      <c r="I163" s="1">
+        <v>0</v>
+      </c>
+      <c r="J163" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
+      <c r="A164" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B164" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C164" t="s">
+      <c r="C164" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D164" t="s">
+      <c r="D164" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E164" t="s">
+      <c r="E164" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="F164" t="s">
-        <v>35</v>
-      </c>
-      <c r="G164" s="2">
+      <c r="F164" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G164" s="3">
         <v>1250000</v>
       </c>
       <c r="H164" s="2">
@@ -6092,25 +6744,25 @@
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
+      <c r="A165" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B165" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C165" t="s">
+      <c r="C165" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D165" t="s">
+      <c r="D165" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="E165" t="s">
+      <c r="E165" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="F165" t="s">
-        <v>35</v>
-      </c>
-      <c r="G165" s="2">
+      <c r="F165" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G165" s="3">
         <v>82117268</v>
       </c>
       <c r="H165" s="2">
@@ -6124,31 +6776,31 @@
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
+      <c r="A166" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B166" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C166" t="s">
+      <c r="C166" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D166" t="s">
+      <c r="D166" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="E166" t="s">
+      <c r="E166" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="F166" t="s">
-        <v>35</v>
-      </c>
-      <c r="G166" s="2">
+      <c r="F166" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G166" s="3">
         <v>12550201</v>
       </c>
-      <c r="H166" s="2">
-        <v>0</v>
-      </c>
-      <c r="I166" s="2">
+      <c r="H166" s="1">
+        <v>0</v>
+      </c>
+      <c r="I166" s="1">
         <v>0</v>
       </c>
       <c r="J166" s="2">
@@ -6156,25 +6808,25 @@
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
+      <c r="A167" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B167" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C167" t="s">
+      <c r="C167" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D167" t="s">
+      <c r="D167" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="E167" t="s">
+      <c r="E167" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F167" t="s">
-        <v>35</v>
-      </c>
-      <c r="G167" s="2">
+      <c r="F167" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G167" s="1">
         <v>0</v>
       </c>
       <c r="H167" s="2">
@@ -6183,30 +6835,30 @@
       <c r="I167" s="2">
         <v>250000</v>
       </c>
-      <c r="J167" s="2">
+      <c r="J167" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
+      <c r="A168" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B168" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C168" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D168" t="s">
+      <c r="D168" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="E168" t="s">
+      <c r="E168" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="F168" t="s">
-        <v>35</v>
-      </c>
-      <c r="G168" s="2">
+      <c r="F168" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G168" s="3">
         <v>15170823</v>
       </c>
       <c r="H168" s="2">
@@ -6220,22 +6872,22 @@
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
+      <c r="A169" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B169" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C169" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D169" t="s">
+      <c r="D169" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="E169" t="s">
+      <c r="E169" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="F169" t="s">
+      <c r="F169" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G169" s="2">
@@ -6252,22 +6904,23 @@
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
+      <c r="A170" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B170" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C170" t="s">
+      <c r="C170" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E170" t="s">
+      <c r="D170" s="1"/>
+      <c r="E170" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="F170" t="s">
-        <v>35</v>
-      </c>
-      <c r="G170" s="2">
+      <c r="F170" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G170" s="1">
         <v>0</v>
       </c>
       <c r="H170" s="2">
@@ -6281,25 +6934,25 @@
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
+      <c r="A171" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B171" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C171" t="s">
+      <c r="C171" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D171" t="s">
+      <c r="D171" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="E171" t="s">
+      <c r="E171" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="F171" t="s">
-        <v>35</v>
-      </c>
-      <c r="G171" s="2">
+      <c r="F171" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G171" s="3">
         <v>500000</v>
       </c>
       <c r="H171" s="2">
@@ -6313,1495 +6966,1548 @@
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
+      <c r="A172" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C172" t="s">
+      <c r="B172" s="1"/>
+      <c r="C172" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D172" t="s">
+      <c r="D172" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="E172" t="s">
+      <c r="E172" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="F172" t="s">
-        <v>12</v>
-      </c>
-      <c r="G172" s="2">
+      <c r="F172" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G172" s="3">
         <v>83145555.510000005</v>
       </c>
-      <c r="H172" s="2">
+      <c r="H172" s="1">
         <v>83145555.510000005</v>
       </c>
-      <c r="I172" s="2">
+      <c r="I172" s="1">
         <v>83145556</v>
       </c>
-      <c r="J172" s="2">
+      <c r="J172" s="1">
         <v>83145555.510000005</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
+      <c r="A173" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C173" t="s">
+      <c r="B173" s="1"/>
+      <c r="C173" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D173" t="s">
+      <c r="D173" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="E173" t="s">
+      <c r="E173" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F173" t="s">
-        <v>12</v>
-      </c>
-      <c r="G173" s="2">
+      <c r="F173" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G173" s="3">
         <v>7871638.1500000004</v>
       </c>
-      <c r="H173" s="2">
+      <c r="H173" s="1">
         <v>7871638.1509999996</v>
       </c>
-      <c r="I173" s="2">
+      <c r="I173" s="1">
         <v>7871638</v>
       </c>
-      <c r="J173" s="2">
+      <c r="J173" s="1">
         <v>7871638.1509999996</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
+      <c r="A174" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C174" t="s">
+      <c r="B174" s="1"/>
+      <c r="C174" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D174" t="s">
+      <c r="D174" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E174" t="s">
+      <c r="E174" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F174" t="s">
-        <v>12</v>
-      </c>
-      <c r="G174" s="2">
-        <v>0</v>
-      </c>
-      <c r="H174" s="2">
-        <v>0</v>
-      </c>
-      <c r="I174" s="2">
-        <v>0</v>
-      </c>
-      <c r="J174" s="2">
+      <c r="F174" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G174" s="1">
+        <v>0</v>
+      </c>
+      <c r="H174" s="1">
+        <v>0</v>
+      </c>
+      <c r="I174" s="1">
+        <v>0</v>
+      </c>
+      <c r="J174" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
+      <c r="A175" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C175" t="s">
+      <c r="B175" s="1"/>
+      <c r="C175" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D175" t="s">
+      <c r="D175" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="E175" t="s">
+      <c r="E175" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F175" t="s">
-        <v>12</v>
-      </c>
-      <c r="G175" s="2">
+      <c r="F175" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G175" s="3">
         <v>10222050</v>
       </c>
-      <c r="H175" s="2">
+      <c r="H175" s="1">
         <v>10222050</v>
       </c>
-      <c r="I175" s="2">
+      <c r="I175" s="1">
         <v>10222050</v>
       </c>
-      <c r="J175" s="2">
+      <c r="J175" s="1">
         <v>10222050</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
+      <c r="A176" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C176" t="s">
+      <c r="B176" s="1"/>
+      <c r="C176" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D176" t="s">
+      <c r="D176" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="E176" t="s">
+      <c r="E176" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="F176" t="s">
-        <v>12</v>
-      </c>
-      <c r="G176" s="2">
+      <c r="F176" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G176" s="1">
         <v>412500</v>
       </c>
-      <c r="H176" s="2">
+      <c r="H176" s="1">
         <v>412500</v>
       </c>
-      <c r="I176" s="2">
+      <c r="I176" s="1">
         <v>412500</v>
       </c>
-      <c r="J176" s="2">
+      <c r="J176" s="1">
         <v>412500</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
+      <c r="A177" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C177" t="s">
+      <c r="B177" s="1"/>
+      <c r="C177" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D177" t="s">
+      <c r="D177" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="E177" t="s">
+      <c r="E177" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="F177" t="s">
-        <v>12</v>
-      </c>
-      <c r="G177" s="2">
-        <v>0</v>
-      </c>
-      <c r="H177" s="2">
-        <v>0</v>
-      </c>
-      <c r="I177" s="2">
-        <v>0</v>
-      </c>
-      <c r="J177" s="2">
+      <c r="F177" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G177" s="1">
+        <v>0</v>
+      </c>
+      <c r="H177" s="1">
+        <v>0</v>
+      </c>
+      <c r="I177" s="1">
+        <v>0</v>
+      </c>
+      <c r="J177" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
+      <c r="A178" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C178" t="s">
+      <c r="B178" s="1"/>
+      <c r="C178" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D178" t="s">
+      <c r="D178" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="E178" t="s">
+      <c r="E178" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="F178" t="s">
-        <v>12</v>
-      </c>
-      <c r="G178" s="2">
+      <c r="F178" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G178" s="3">
         <v>1198950</v>
       </c>
-      <c r="H178" s="2">
+      <c r="H178" s="1">
         <v>1198950</v>
       </c>
-      <c r="I178" s="2">
+      <c r="I178" s="1">
         <v>1198950</v>
       </c>
-      <c r="J178" s="2">
+      <c r="J178" s="1">
         <v>1198950</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
+      <c r="A179" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C179" t="s">
+      <c r="B179" s="1"/>
+      <c r="C179" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D179" t="s">
+      <c r="D179" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="E179" t="s">
+      <c r="E179" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="F179" t="s">
-        <v>12</v>
-      </c>
-      <c r="G179" s="2">
+      <c r="F179" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G179" s="3">
         <v>5530049.9500000002</v>
       </c>
-      <c r="H179" s="2">
+      <c r="H179" s="1">
         <v>5530049.9510000004</v>
       </c>
-      <c r="I179" s="2">
+      <c r="I179" s="1">
         <v>5530050</v>
       </c>
-      <c r="J179" s="2">
+      <c r="J179" s="1">
         <v>5530049.9510000004</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
+      <c r="A180" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C180" t="s">
+      <c r="B180" s="1"/>
+      <c r="C180" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D180" t="s">
+      <c r="D180" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="E180" t="s">
+      <c r="E180" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="F180" t="s">
-        <v>12</v>
-      </c>
-      <c r="G180" s="2">
+      <c r="F180" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G180" s="3">
         <v>270701.25</v>
       </c>
-      <c r="H180" s="2">
+      <c r="H180" s="1">
         <v>270701.25</v>
       </c>
-      <c r="I180" s="2">
+      <c r="I180" s="1">
         <v>270701.3</v>
       </c>
-      <c r="J180" s="2">
+      <c r="J180" s="1">
         <v>270701.25</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
+      <c r="A181" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C181" t="s">
+      <c r="B181" s="1"/>
+      <c r="C181" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D181" t="s">
+      <c r="D181" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E181" t="s">
+      <c r="E181" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="F181" t="s">
-        <v>12</v>
-      </c>
-      <c r="G181" s="2">
-        <v>0</v>
-      </c>
-      <c r="H181" s="2">
-        <v>0</v>
-      </c>
-      <c r="I181" s="2">
-        <v>0</v>
-      </c>
-      <c r="J181" s="2">
+      <c r="F181" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G181" s="1">
+        <v>0</v>
+      </c>
+      <c r="H181" s="1">
+        <v>0</v>
+      </c>
+      <c r="I181" s="1">
+        <v>0</v>
+      </c>
+      <c r="J181" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
+      <c r="A182" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C182" t="s">
+      <c r="B182" s="1"/>
+      <c r="C182" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D182" t="s">
+      <c r="D182" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="E182" t="s">
+      <c r="E182" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="F182" t="s">
-        <v>12</v>
-      </c>
-      <c r="G182" s="2">
+      <c r="F182" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G182" s="3">
         <v>1312500</v>
       </c>
-      <c r="H182" s="2">
+      <c r="H182" s="1">
         <v>1312500</v>
       </c>
-      <c r="I182" s="2">
+      <c r="I182" s="1">
         <v>1312500</v>
       </c>
-      <c r="J182" s="2">
+      <c r="J182" s="1">
         <v>1312500</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
+      <c r="A183" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C183" t="s">
+      <c r="B183" s="1"/>
+      <c r="C183" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="D183" t="s">
+      <c r="D183" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E183" t="s">
+      <c r="E183" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="F183" t="s">
-        <v>12</v>
-      </c>
-      <c r="G183" s="2">
+      <c r="F183" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G183" s="1">
         <v>4941349.0360000003</v>
       </c>
-      <c r="H183" s="2">
+      <c r="H183" s="1">
         <v>4941349.0360000003</v>
       </c>
-      <c r="I183" s="2">
+      <c r="I183" s="1">
         <v>4941349</v>
       </c>
-      <c r="J183" s="2">
+      <c r="J183" s="1">
         <v>4941349.0360000003</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
+      <c r="A184" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C184" t="s">
+      <c r="B184" s="1"/>
+      <c r="C184" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="D184" t="s">
+      <c r="D184" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="E184" t="s">
+      <c r="E184" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="F184" t="s">
-        <v>12</v>
-      </c>
-      <c r="G184" s="2">
+      <c r="F184" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G184" s="3">
         <v>300442.40999999997</v>
       </c>
-      <c r="H184" s="2">
+      <c r="H184" s="1">
         <v>300442.40509999997</v>
       </c>
-      <c r="I184" s="2">
+      <c r="I184" s="1">
         <v>300442.40000000002</v>
       </c>
-      <c r="J184" s="2">
+      <c r="J184" s="1">
         <v>300442.40509999997</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
+      <c r="A185" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C185" t="s">
+      <c r="B185" s="1"/>
+      <c r="C185" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D185" t="s">
+      <c r="D185" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="E185" t="s">
+      <c r="E185" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="F185" t="s">
-        <v>12</v>
-      </c>
-      <c r="G185" s="2">
+      <c r="F185" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G185" s="3">
         <v>15831702</v>
       </c>
-      <c r="H185" s="2">
+      <c r="H185" s="1">
         <v>15831702</v>
       </c>
-      <c r="I185" s="2">
+      <c r="I185" s="1">
         <v>15831702</v>
       </c>
-      <c r="J185" s="2">
+      <c r="J185" s="1">
         <v>15831702</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
+      <c r="A186" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C186" t="s">
+      <c r="B186" s="1"/>
+      <c r="C186" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D186" t="s">
+      <c r="D186" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="E186" t="s">
+      <c r="E186" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="F186" t="s">
+      <c r="F186" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G186" s="2">
         <v>3062216</v>
       </c>
-      <c r="H186" s="2">
+      <c r="H186" s="1">
         <v>3062215.6320000002</v>
       </c>
-      <c r="I186" s="2">
+      <c r="I186" s="1">
         <v>3062216</v>
       </c>
-      <c r="J186" s="2">
+      <c r="J186" s="1">
         <v>3062215.6320000002</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
+      <c r="A187" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C187" t="s">
+      <c r="B187" s="1"/>
+      <c r="C187" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D187" t="s">
+      <c r="D187" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="E187" t="s">
+      <c r="E187" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="F187" t="s">
+      <c r="F187" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G187" s="2">
         <v>700518</v>
       </c>
-      <c r="H187" s="2">
+      <c r="H187" s="1">
         <v>700517.7855</v>
       </c>
-      <c r="I187" s="2">
+      <c r="I187" s="1">
         <v>700517.8</v>
       </c>
-      <c r="J187" s="2">
+      <c r="J187" s="1">
         <v>700517.7855</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
+      <c r="A188" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C188" t="s">
+      <c r="B188" s="1"/>
+      <c r="C188" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D188" t="s">
+      <c r="D188" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E188" t="s">
+      <c r="E188" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="F188" t="s">
-        <v>12</v>
-      </c>
-      <c r="G188" s="2">
+      <c r="F188" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G188" s="1">
         <v>2527388.699</v>
       </c>
-      <c r="H188" s="2">
+      <c r="H188" s="1">
         <v>2527388.699</v>
       </c>
-      <c r="I188" s="2">
+      <c r="I188" s="1">
         <v>2527389</v>
       </c>
-      <c r="J188" s="2">
+      <c r="J188" s="1">
         <v>2527388.699</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
+      <c r="A189" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C189" t="s">
+      <c r="B189" s="1"/>
+      <c r="C189" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D189" t="s">
+      <c r="D189" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="E189" t="s">
+      <c r="E189" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="F189" t="s">
+      <c r="F189" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G189" s="2">
         <v>76073690</v>
       </c>
-      <c r="H189" s="2">
+      <c r="H189" s="1">
         <v>76073690.480000004</v>
       </c>
-      <c r="I189" s="2">
+      <c r="I189" s="1">
         <v>76073690</v>
       </c>
-      <c r="J189" s="2">
+      <c r="J189" s="1">
         <v>76073690.480000004</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
+      <c r="A190" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C190" t="s">
+      <c r="B190" s="1"/>
+      <c r="C190" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D190" t="s">
+      <c r="D190" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="E190" t="s">
+      <c r="E190" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F190" t="s">
+      <c r="F190" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G190" s="2">
         <v>7387369</v>
       </c>
-      <c r="H190" s="2">
+      <c r="H190" s="1">
         <v>7387369.0480000004</v>
       </c>
-      <c r="I190" s="2">
+      <c r="I190" s="1">
         <v>7387369</v>
       </c>
-      <c r="J190" s="2">
+      <c r="J190" s="1">
         <v>7387369.0480000004</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
+      <c r="A191" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C191" t="s">
+      <c r="B191" s="1"/>
+      <c r="C191" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D191" t="s">
+      <c r="D191" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E191" t="s">
+      <c r="E191" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F191" t="s">
-        <v>35</v>
-      </c>
-      <c r="G191" s="2">
-        <v>0</v>
-      </c>
-      <c r="H191" s="2">
-        <v>0</v>
-      </c>
-      <c r="I191" s="2">
-        <v>0</v>
-      </c>
-      <c r="J191" s="2">
+      <c r="F191" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G191" s="1">
+        <v>0</v>
+      </c>
+      <c r="H191" s="1">
+        <v>0</v>
+      </c>
+      <c r="I191" s="1">
+        <v>0</v>
+      </c>
+      <c r="J191" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
+      <c r="A192" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C192" t="s">
+      <c r="B192" s="1"/>
+      <c r="C192" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D192" t="s">
+      <c r="D192" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="E192" t="s">
+      <c r="E192" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F192" t="s">
+      <c r="F192" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G192" s="2">
         <v>9357450</v>
       </c>
-      <c r="H192" s="2">
+      <c r="H192" s="1">
         <v>9357450</v>
       </c>
-      <c r="I192" s="2">
+      <c r="I192" s="1">
         <v>9357450</v>
       </c>
-      <c r="J192" s="2">
+      <c r="J192" s="1">
         <v>9357450</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
+      <c r="A193" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C193" t="s">
+      <c r="B193" s="1"/>
+      <c r="C193" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D193" t="s">
+      <c r="D193" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="E193" t="s">
+      <c r="E193" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="F193" t="s">
+      <c r="F193" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G193" s="2">
         <v>468750</v>
       </c>
-      <c r="H193" s="2">
+      <c r="H193" s="1">
         <v>468750</v>
       </c>
-      <c r="I193" s="2">
+      <c r="I193" s="1">
         <v>468750</v>
       </c>
-      <c r="J193" s="2">
+      <c r="J193" s="1">
         <v>468750</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
+      <c r="A194" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C194" t="s">
+      <c r="B194" s="1"/>
+      <c r="C194" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D194" t="s">
+      <c r="D194" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="E194" t="s">
+      <c r="E194" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="F194" t="s">
-        <v>35</v>
-      </c>
-      <c r="G194" s="2">
-        <v>0</v>
-      </c>
-      <c r="H194" s="2">
-        <v>0</v>
-      </c>
-      <c r="I194" s="2">
-        <v>0</v>
-      </c>
-      <c r="J194" s="2">
+      <c r="F194" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G194" s="1">
+        <v>0</v>
+      </c>
+      <c r="H194" s="1">
+        <v>0</v>
+      </c>
+      <c r="I194" s="1">
+        <v>0</v>
+      </c>
+      <c r="J194" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
+      <c r="A195" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C195" t="s">
+      <c r="B195" s="1"/>
+      <c r="C195" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D195" t="s">
+      <c r="D195" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="E195" t="s">
+      <c r="E195" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="F195" t="s">
+      <c r="F195" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G195" s="2">
         <v>1098300</v>
       </c>
-      <c r="H195" s="2">
+      <c r="H195" s="1">
         <v>1098300</v>
       </c>
-      <c r="I195" s="2">
+      <c r="I195" s="1">
         <v>1098300</v>
       </c>
-      <c r="J195" s="2">
+      <c r="J195" s="1">
         <v>1098300</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
+      <c r="A196" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C196" t="s">
+      <c r="B196" s="1"/>
+      <c r="C196" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D196" t="s">
+      <c r="D196" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="E196" t="s">
+      <c r="E196" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="F196" t="s">
+      <c r="F196" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G196" s="2">
         <v>5654776</v>
       </c>
-      <c r="H196" s="2">
+      <c r="H196" s="1">
         <v>5654775.7379999999</v>
       </c>
-      <c r="I196" s="2">
+      <c r="I196" s="1">
         <v>5654776</v>
       </c>
-      <c r="J196" s="2">
+      <c r="J196" s="1">
         <v>5654775.7379999999</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
+      <c r="A197" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C197" t="s">
+      <c r="B197" s="1"/>
+      <c r="C197" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D197" t="s">
+      <c r="D197" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="E197" t="s">
+      <c r="E197" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="F197" t="s">
+      <c r="F197" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G197" s="2">
         <v>242674</v>
       </c>
-      <c r="H197" s="2">
+      <c r="H197" s="1">
         <v>242673.75</v>
       </c>
-      <c r="I197" s="2">
+      <c r="I197" s="1">
         <v>242673.8</v>
       </c>
-      <c r="J197" s="2">
+      <c r="J197" s="1">
         <v>242673.75</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
+      <c r="A198" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C198" t="s">
+      <c r="B198" s="1"/>
+      <c r="C198" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D198" t="s">
+      <c r="D198" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E198" t="s">
+      <c r="E198" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="F198" t="s">
-        <v>35</v>
-      </c>
-      <c r="G198" s="2">
-        <v>0</v>
-      </c>
-      <c r="H198" s="2">
-        <v>0</v>
-      </c>
-      <c r="I198" s="2">
-        <v>0</v>
-      </c>
-      <c r="J198" s="2">
+      <c r="F198" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G198" s="1">
+        <v>0</v>
+      </c>
+      <c r="H198" s="1">
+        <v>0</v>
+      </c>
+      <c r="I198" s="1">
+        <v>0</v>
+      </c>
+      <c r="J198" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
+      <c r="A199" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C199" t="s">
+      <c r="B199" s="1"/>
+      <c r="C199" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D199" t="s">
+      <c r="D199" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="E199" t="s">
+      <c r="E199" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="F199" t="s">
+      <c r="F199" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G199" s="2">
         <v>1312500</v>
       </c>
-      <c r="H199" s="2">
+      <c r="H199" s="1">
         <v>1312500</v>
       </c>
-      <c r="I199" s="2">
+      <c r="I199" s="1">
         <v>1312500</v>
       </c>
-      <c r="J199" s="2">
+      <c r="J199" s="1">
         <v>1312500</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
+      <c r="A200" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C200" t="s">
+      <c r="B200" s="1"/>
+      <c r="C200" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="D200" t="s">
+      <c r="D200" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E200" t="s">
+      <c r="E200" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="F200" t="s">
+      <c r="F200" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G200" s="2">
         <v>4405520</v>
       </c>
-      <c r="H200" s="2">
+      <c r="H200" s="1">
         <v>4405520.2640000004</v>
       </c>
-      <c r="I200" s="2">
+      <c r="I200" s="1">
         <v>4405520</v>
       </c>
-      <c r="J200" s="2">
+      <c r="J200" s="1">
         <v>4405520.2640000004</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
+      <c r="A201" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C201" t="s">
+      <c r="B201" s="1"/>
+      <c r="C201" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="D201" t="s">
+      <c r="D201" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="E201" t="s">
+      <c r="E201" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="F201" t="s">
+      <c r="F201" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G201" s="2">
         <v>269567</v>
       </c>
-      <c r="H201" s="2">
+      <c r="H201" s="1">
         <v>269566.90100000001</v>
       </c>
-      <c r="I201" s="2">
+      <c r="I201" s="1">
         <v>269566.90000000002</v>
       </c>
-      <c r="J201" s="2">
+      <c r="J201" s="1">
         <v>269566.90100000001</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
+      <c r="A202" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C202" t="s">
+      <c r="B202" s="1"/>
+      <c r="C202" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D202" t="s">
+      <c r="D202" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="E202" t="s">
+      <c r="E202" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="F202" t="s">
+      <c r="F202" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G202" s="2">
         <v>13269084</v>
       </c>
-      <c r="H202" s="2">
+      <c r="H202" s="1">
         <v>13269083.949999999</v>
       </c>
-      <c r="I202" s="2">
+      <c r="I202" s="1">
         <v>13269084</v>
       </c>
-      <c r="J202" s="2">
+      <c r="J202" s="1">
         <v>13269083.949999999</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
+      <c r="A203" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C203" t="s">
+      <c r="B203" s="1"/>
+      <c r="C203" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D203" t="s">
+      <c r="D203" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="E203" t="s">
+      <c r="E203" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="F203" t="s">
+      <c r="F203" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G203" s="2">
         <v>3008212</v>
       </c>
-      <c r="H203" s="2">
+      <c r="H203" s="1">
         <v>3008211.9219999998</v>
       </c>
-      <c r="I203" s="2">
+      <c r="I203" s="1">
         <v>3008212</v>
       </c>
-      <c r="J203" s="2">
+      <c r="J203" s="1">
         <v>3008211.9219999998</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
+      <c r="A204" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C204" t="s">
+      <c r="B204" s="1"/>
+      <c r="C204" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D204" t="s">
+      <c r="D204" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="E204" t="s">
+      <c r="E204" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="F204" t="s">
+      <c r="F204" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G204" s="2">
         <v>587128</v>
       </c>
-      <c r="H204" s="2">
+      <c r="H204" s="1">
         <v>587127.60849999997</v>
       </c>
-      <c r="I204" s="2">
+      <c r="I204" s="1">
         <v>587127.6</v>
       </c>
-      <c r="J204" s="2">
+      <c r="J204" s="1">
         <v>587127.60849999997</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
+      <c r="A205" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C205" t="s">
+      <c r="B205" s="1"/>
+      <c r="C205" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D205" t="s">
+      <c r="D205" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E205" t="s">
+      <c r="E205" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="F205" t="s">
+      <c r="F205" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G205" s="2">
         <v>2241892</v>
       </c>
-      <c r="H205" s="2">
+      <c r="H205" s="1">
         <v>2241892.1230000001</v>
       </c>
-      <c r="I205" s="2">
+      <c r="I205" s="1">
         <v>2241892</v>
       </c>
-      <c r="J205" s="2">
+      <c r="J205" s="1">
         <v>2241892.1230000001</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
+      <c r="A206" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C206" t="s">
+      <c r="B206" s="1"/>
+      <c r="C206" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D206" t="s">
+      <c r="D206" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="E206" t="s">
+      <c r="E206" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="F206" t="s">
+      <c r="F206" s="1" t="s">
         <v>192</v>
       </c>
       <c r="G206" s="2">
         <v>4426132</v>
       </c>
-      <c r="H206" s="2">
+      <c r="H206" s="1">
         <v>4426131.5999999996</v>
       </c>
-      <c r="I206" s="2">
+      <c r="I206" s="1">
         <v>4426132</v>
       </c>
-      <c r="J206" s="2">
+      <c r="J206" s="1">
         <v>4426131.5999999996</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
+      <c r="A207" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C207" t="s">
+      <c r="B207" s="1"/>
+      <c r="C207" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D207" t="s">
+      <c r="D207" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="E207" t="s">
+      <c r="E207" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F207" t="s">
+      <c r="F207" s="1" t="s">
         <v>192</v>
       </c>
       <c r="G207" s="2">
         <v>442613</v>
       </c>
-      <c r="H207" s="2">
+      <c r="H207" s="1">
         <v>442613.16</v>
       </c>
-      <c r="I207" s="2">
+      <c r="I207" s="1">
         <v>442613.2</v>
       </c>
-      <c r="J207" s="2">
+      <c r="J207" s="1">
         <v>442613.16</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
+      <c r="A208" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C208" t="s">
+      <c r="B208" s="1"/>
+      <c r="C208" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D208" t="s">
+      <c r="D208" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E208" t="s">
+      <c r="E208" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F208" t="s">
+      <c r="F208" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="G208" s="2">
-        <v>0</v>
-      </c>
-      <c r="H208" s="2">
-        <v>0</v>
-      </c>
-      <c r="I208" s="2">
-        <v>0</v>
-      </c>
-      <c r="J208" s="2">
+      <c r="G208" s="1">
+        <v>0</v>
+      </c>
+      <c r="H208" s="1">
+        <v>0</v>
+      </c>
+      <c r="I208" s="1">
+        <v>0</v>
+      </c>
+      <c r="J208" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
+      <c r="A209" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C209" t="s">
+      <c r="B209" s="1"/>
+      <c r="C209" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D209" t="s">
+      <c r="D209" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="E209" t="s">
+      <c r="E209" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F209" t="s">
+      <c r="F209" s="1" t="s">
         <v>192</v>
       </c>
       <c r="G209" s="2">
         <v>732000</v>
       </c>
-      <c r="H209" s="2">
+      <c r="H209" s="1">
         <v>732000</v>
       </c>
-      <c r="I209" s="2">
+      <c r="I209" s="1">
         <v>732000</v>
       </c>
-      <c r="J209" s="2">
+      <c r="J209" s="1">
         <v>732000</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
+      <c r="A210" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C210" t="s">
+      <c r="B210" s="1"/>
+      <c r="C210" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D210" t="s">
+      <c r="D210" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="E210" t="s">
+      <c r="E210" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="F210" t="s">
+      <c r="F210" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="G210" s="2">
-        <v>0</v>
-      </c>
-      <c r="H210" s="2">
-        <v>0</v>
-      </c>
-      <c r="I210" s="2">
-        <v>0</v>
-      </c>
-      <c r="J210" s="2">
+      <c r="G210" s="1">
+        <v>0</v>
+      </c>
+      <c r="H210" s="1">
+        <v>0</v>
+      </c>
+      <c r="I210" s="1">
+        <v>0</v>
+      </c>
+      <c r="J210" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
+      <c r="A211" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C211" t="s">
+      <c r="B211" s="1"/>
+      <c r="C211" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D211" t="s">
+      <c r="D211" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="E211" t="s">
+      <c r="E211" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="F211" t="s">
+      <c r="F211" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="G211" s="2">
-        <v>0</v>
-      </c>
-      <c r="H211" s="2">
-        <v>0</v>
-      </c>
-      <c r="I211" s="2">
-        <v>0</v>
-      </c>
-      <c r="J211" s="2">
+      <c r="G211" s="1">
+        <v>0</v>
+      </c>
+      <c r="H211" s="1">
+        <v>0</v>
+      </c>
+      <c r="I211" s="1">
+        <v>0</v>
+      </c>
+      <c r="J211" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
+      <c r="A212" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C212" t="s">
+      <c r="B212" s="1"/>
+      <c r="C212" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D212" t="s">
+      <c r="D212" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="E212" t="s">
+      <c r="E212" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="F212" t="s">
+      <c r="F212" s="1" t="s">
         <v>192</v>
       </c>
       <c r="G212" s="2">
         <v>72000</v>
       </c>
-      <c r="H212" s="2">
+      <c r="H212" s="1">
         <v>72000</v>
       </c>
-      <c r="I212" s="2">
+      <c r="I212" s="1">
         <v>72000</v>
       </c>
-      <c r="J212" s="2">
+      <c r="J212" s="1">
         <v>72000</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
+      <c r="A213" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C213" t="s">
+      <c r="B213" s="1"/>
+      <c r="C213" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D213" t="s">
+      <c r="D213" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="E213" t="s">
+      <c r="E213" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="F213" t="s">
+      <c r="F213" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="G213" s="2">
+      <c r="G213" s="1">
         <v>368844.3</v>
       </c>
-      <c r="H213" s="2">
+      <c r="H213" s="1">
         <v>368844.3</v>
       </c>
-      <c r="I213" s="2">
+      <c r="I213" s="1">
         <v>368844.3</v>
       </c>
-      <c r="J213" s="2">
+      <c r="J213" s="1">
         <v>368844.3</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
+      <c r="A214" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C214" t="s">
+      <c r="B214" s="1"/>
+      <c r="C214" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D214" t="s">
+      <c r="D214" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="E214" t="s">
+      <c r="E214" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="F214" t="s">
+      <c r="F214" s="1" t="s">
         <v>192</v>
       </c>
       <c r="G214" s="2">
         <v>11100</v>
       </c>
-      <c r="H214" s="2">
+      <c r="H214" s="1">
         <v>11100</v>
       </c>
-      <c r="I214" s="2">
+      <c r="I214" s="1">
         <v>11100</v>
       </c>
-      <c r="J214" s="2">
+      <c r="J214" s="1">
         <v>11100</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
+      <c r="A215" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C215" t="s">
+      <c r="B215" s="1"/>
+      <c r="C215" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D215" t="s">
+      <c r="D215" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E215" t="s">
+      <c r="E215" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="F215" t="s">
+      <c r="F215" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="G215" s="2">
-        <v>0</v>
-      </c>
-      <c r="H215" s="2">
-        <v>0</v>
-      </c>
-      <c r="I215" s="2">
-        <v>0</v>
-      </c>
-      <c r="J215" s="2">
+      <c r="G215" s="1">
+        <v>0</v>
+      </c>
+      <c r="H215" s="1">
+        <v>0</v>
+      </c>
+      <c r="I215" s="1">
+        <v>0</v>
+      </c>
+      <c r="J215" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
+      <c r="A216" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C216" t="s">
+      <c r="B216" s="1"/>
+      <c r="C216" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D216" t="s">
+      <c r="D216" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="E216" t="s">
+      <c r="E216" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="F216" t="s">
+      <c r="F216" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="G216" s="2">
-        <v>0</v>
-      </c>
-      <c r="H216" s="2">
-        <v>0</v>
-      </c>
-      <c r="I216" s="2">
-        <v>0</v>
-      </c>
-      <c r="J216" s="2">
+      <c r="G216" s="1">
+        <v>0</v>
+      </c>
+      <c r="H216" s="1">
+        <v>0</v>
+      </c>
+      <c r="I216" s="1">
+        <v>0</v>
+      </c>
+      <c r="J216" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
+      <c r="A217" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C217" t="s">
+      <c r="B217" s="1"/>
+      <c r="C217" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="D217" t="s">
+      <c r="D217" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E217" t="s">
+      <c r="E217" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="F217" t="s">
+      <c r="F217" s="1" t="s">
         <v>192</v>
       </c>
       <c r="G217" s="2">
         <v>197412</v>
       </c>
-      <c r="H217" s="2">
+      <c r="H217" s="1">
         <v>197411.9</v>
       </c>
-      <c r="I217" s="2">
+      <c r="I217" s="1">
         <v>197411.9</v>
       </c>
-      <c r="J217" s="2">
+      <c r="J217" s="1">
         <v>197411.9</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
+      <c r="A218" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C218" t="s">
+      <c r="B218" s="1"/>
+      <c r="C218" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="D218" t="s">
+      <c r="D218" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="E218" t="s">
+      <c r="E218" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="F218" t="s">
+      <c r="F218" s="1" t="s">
         <v>192</v>
       </c>
       <c r="G218" s="2">
         <v>11875</v>
       </c>
-      <c r="H218" s="2">
+      <c r="H218" s="1">
         <v>11875.193880000001</v>
       </c>
-      <c r="I218" s="2">
+      <c r="I218" s="1">
         <v>11875.19</v>
       </c>
-      <c r="J218" s="2">
+      <c r="J218" s="1">
         <v>11875.193880000001</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
+      <c r="A219" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C219" t="s">
+      <c r="B219" s="1"/>
+      <c r="C219" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D219" t="s">
+      <c r="D219" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="E219" t="s">
+      <c r="E219" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="F219" t="s">
+      <c r="F219" s="1" t="s">
         <v>192</v>
       </c>
       <c r="G219" s="2">
         <v>854302</v>
       </c>
-      <c r="H219" s="2">
+      <c r="H219" s="1">
         <v>854301.5</v>
       </c>
-      <c r="I219" s="2">
+      <c r="I219" s="1">
         <v>854301.5</v>
       </c>
-      <c r="J219" s="2">
+      <c r="J219" s="1">
         <v>854301.5</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
+      <c r="A220" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C220" t="s">
+      <c r="B220" s="1"/>
+      <c r="C220" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D220" t="s">
+      <c r="D220" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="E220" t="s">
+      <c r="E220" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="F220" t="s">
+      <c r="F220" s="1" t="s">
         <v>192</v>
       </c>
       <c r="G220" s="2">
         <v>671451</v>
       </c>
-      <c r="H220" s="2">
+      <c r="H220" s="1">
         <v>671450.80260000005</v>
       </c>
-      <c r="I220" s="2">
+      <c r="I220" s="1">
         <v>671450.8</v>
       </c>
-      <c r="J220" s="2">
+      <c r="J220" s="1">
         <v>671450.80260000005</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
+      <c r="A221" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C221" t="s">
+      <c r="B221" s="1"/>
+      <c r="C221" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D221" t="s">
+      <c r="D221" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="E221" t="s">
+      <c r="E221" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="F221" t="s">
+      <c r="F221" s="1" t="s">
         <v>192</v>
       </c>
       <c r="G221" s="2">
         <v>37801</v>
       </c>
-      <c r="H221" s="2">
+      <c r="H221" s="1">
         <v>37800.950689999998</v>
       </c>
-      <c r="I221" s="2">
+      <c r="I221" s="1">
         <v>37800.949999999997</v>
       </c>
-      <c r="J221" s="2">
+      <c r="J221" s="1">
         <v>37800.950689999998</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
+      <c r="A222" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C222" t="s">
+      <c r="B222" s="1"/>
+      <c r="C222" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D222" t="s">
+      <c r="D222" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E222" t="s">
+      <c r="E222" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="F222" t="s">
+      <c r="F222" s="1" t="s">
         <v>192</v>
       </c>
       <c r="G222" s="2">
         <v>140625</v>
       </c>
-      <c r="H222" s="2">
+      <c r="H222" s="1">
         <v>140625</v>
       </c>
-      <c r="I222" s="2">
+      <c r="I222" s="1">
         <v>140625</v>
       </c>
-      <c r="J222" s="2">
+      <c r="J222" s="1">
         <v>140625</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
+      <c r="A223" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C223" t="s">
+      <c r="B223" s="1"/>
+      <c r="C223" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="E223" t="s">
+      <c r="D223" s="1"/>
+      <c r="E223" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="F223" t="s">
+      <c r="F223" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G223" s="2">
@@ -7810,24 +8516,26 @@
       <c r="H223" s="2">
         <v>3250000</v>
       </c>
-      <c r="I223" s="2">
-        <v>0</v>
-      </c>
-      <c r="J223" s="2">
+      <c r="I223" s="1">
+        <v>0</v>
+      </c>
+      <c r="J223" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
+      <c r="A224" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C224" t="s">
+      <c r="B224" s="1"/>
+      <c r="C224" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="E224" t="s">
+      <c r="D224" s="1"/>
+      <c r="E224" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="F224" t="s">
+      <c r="F224" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G224" s="2">
@@ -7836,24 +8544,26 @@
       <c r="H224" s="2">
         <v>515000</v>
       </c>
-      <c r="I224" s="2">
-        <v>0</v>
-      </c>
-      <c r="J224" s="2">
+      <c r="I224" s="1">
+        <v>0</v>
+      </c>
+      <c r="J224" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
+      <c r="A225" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C225" t="s">
+      <c r="B225" s="1"/>
+      <c r="C225" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="E225" t="s">
+      <c r="D225" s="1"/>
+      <c r="E225" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="F225" t="s">
+      <c r="F225" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G225" s="2">
@@ -7862,24 +8572,26 @@
       <c r="H225" s="2">
         <v>450000</v>
       </c>
-      <c r="I225" s="2">
-        <v>0</v>
-      </c>
-      <c r="J225" s="2">
+      <c r="I225" s="1">
+        <v>0</v>
+      </c>
+      <c r="J225" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
+      <c r="A226" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C226" t="s">
+      <c r="B226" s="1"/>
+      <c r="C226" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="E226" t="s">
+      <c r="D226" s="1"/>
+      <c r="E226" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="F226" t="s">
+      <c r="F226" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G226" s="2">
@@ -7888,24 +8600,26 @@
       <c r="H226" s="2">
         <v>1200000</v>
       </c>
-      <c r="I226" s="2">
+      <c r="I226" s="1">
         <v>1331250</v>
       </c>
-      <c r="J226" s="2">
+      <c r="J226" s="1">
         <v>1331250</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
+      <c r="A227" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C227" t="s">
+      <c r="B227" s="1"/>
+      <c r="C227" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="E227" t="s">
+      <c r="D227" s="1"/>
+      <c r="E227" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="F227" t="s">
+      <c r="F227" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G227" s="2">
@@ -7914,24 +8628,26 @@
       <c r="H227" s="2">
         <v>4375000</v>
       </c>
-      <c r="I227" s="2">
+      <c r="I227" s="1">
         <v>250000</v>
       </c>
-      <c r="J227" s="2">
+      <c r="J227" s="1">
         <v>250000</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
+      <c r="A228" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C228" t="s">
+      <c r="B228" s="1"/>
+      <c r="C228" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="E228" t="s">
+      <c r="D228" s="1"/>
+      <c r="E228" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="F228" t="s">
+      <c r="F228" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G228" s="2">
@@ -7940,24 +8656,26 @@
       <c r="H228" s="2">
         <v>3250000</v>
       </c>
-      <c r="I228" s="2">
-        <v>0</v>
-      </c>
-      <c r="J228" s="2">
+      <c r="I228" s="1">
+        <v>0</v>
+      </c>
+      <c r="J228" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
+      <c r="A229" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C229" t="s">
+      <c r="B229" s="1"/>
+      <c r="C229" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="E229" t="s">
+      <c r="D229" s="1"/>
+      <c r="E229" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="F229" t="s">
+      <c r="F229" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G229" s="2">
@@ -7966,24 +8684,26 @@
       <c r="H229" s="2">
         <v>515000</v>
       </c>
-      <c r="I229" s="2">
-        <v>0</v>
-      </c>
-      <c r="J229" s="2">
+      <c r="I229" s="1">
+        <v>0</v>
+      </c>
+      <c r="J229" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
+      <c r="A230" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C230" t="s">
+      <c r="B230" s="1"/>
+      <c r="C230" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="E230" t="s">
+      <c r="D230" s="1"/>
+      <c r="E230" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="F230" t="s">
+      <c r="F230" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G230" s="2">
@@ -7992,24 +8712,26 @@
       <c r="H230" s="2">
         <v>450000</v>
       </c>
-      <c r="I230" s="2">
-        <v>0</v>
-      </c>
-      <c r="J230" s="2">
+      <c r="I230" s="1">
+        <v>0</v>
+      </c>
+      <c r="J230" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
+      <c r="A231" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C231" t="s">
+      <c r="B231" s="1"/>
+      <c r="C231" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="E231" t="s">
+      <c r="D231" s="1"/>
+      <c r="E231" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="F231" t="s">
+      <c r="F231" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G231" s="2">
@@ -8018,24 +8740,26 @@
       <c r="H231" s="2">
         <v>1200000</v>
       </c>
-      <c r="I231" s="2">
+      <c r="I231" s="1">
         <v>1331250</v>
       </c>
-      <c r="J231" s="2">
+      <c r="J231" s="1">
         <v>1331250</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
+      <c r="A232" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C232" t="s">
+      <c r="B232" s="1"/>
+      <c r="C232" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="E232" t="s">
+      <c r="D232" s="1"/>
+      <c r="E232" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="F232" t="s">
+      <c r="F232" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G232" s="2">
@@ -8044,15 +8768,15 @@
       <c r="H232" s="2">
         <v>4375000</v>
       </c>
-      <c r="I232" s="2">
+      <c r="I232" s="1">
         <v>250000</v>
       </c>
-      <c r="J232" s="2">
+      <c r="J232" s="1">
         <v>250000</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J232" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:J232" xr:uid="{1417D1F6-F6B4-48AE-8FD9-EF6F6F73215F}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>